--- a/Bases_de_Dados/FootyStats/South Africa Premier Soccer League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/South Africa Premier Soccer League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP145"/>
+  <dimension ref="A1:BP146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.67</v>
@@ -3966,7 +3966,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR19" t="n">
         <v>1.47</v>
@@ -4835,7 +4835,7 @@
         <v>3</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ20" t="n">
         <v>2</v>
@@ -7890,7 +7890,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR34" t="n">
         <v>1.52</v>
@@ -8977,7 +8977,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.73</v>
@@ -11814,7 +11814,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR52" t="n">
         <v>1.09</v>
@@ -12247,7 +12247,7 @@
         <v>1</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.5</v>
@@ -13555,7 +13555,7 @@
         <v>1.33</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.44</v>
@@ -14866,7 +14866,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR66" t="n">
         <v>2.23</v>
@@ -18351,7 +18351,7 @@
         <v>0.2</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.4</v>
@@ -18572,7 +18572,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR83" t="n">
         <v>1.52</v>
@@ -19444,7 +19444,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR87" t="n">
         <v>1.89</v>
@@ -22275,7 +22275,7 @@
         <v>0.4</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ100" t="n">
         <v>1.38</v>
@@ -24019,7 +24019,7 @@
         <v>0.86</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ108" t="n">
         <v>1</v>
@@ -26199,7 +26199,7 @@
         <v>0.29</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.67</v>
@@ -29908,7 +29908,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR135" t="n">
         <v>0.92</v>
@@ -32106,13 +32106,13 @@
         <v>1</v>
       </c>
       <c r="AW145" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX145" t="n">
         <v>5</v>
       </c>
       <c r="AY145" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ145" t="n">
         <v>6</v>
@@ -32164,6 +32164,224 @@
       </c>
       <c r="BP145" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="n">
+        <v>8149608</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>46081.63541666666</v>
+      </c>
+      <c r="F146" t="n">
+        <v>19</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Orbit College</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Richards Bay</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R146" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S146" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="T146" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U146" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V146" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W146" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X146" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT146" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB146" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE146" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="BF146" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG146" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BH146" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BI146" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BJ146" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BK146" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BL146" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BM146" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BN146" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BO146" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="BP146" t="n">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/South Africa Premier Soccer League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/South Africa Premier Soccer League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP146"/>
+  <dimension ref="A1:BP148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,7 +1786,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.2</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ12" t="n">
         <v>2.22</v>
@@ -4838,7 +4838,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR20" t="n">
         <v>0.87</v>
@@ -7018,7 +7018,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR30" t="n">
         <v>1.27</v>
@@ -8544,7 +8544,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR37" t="n">
         <v>1.99</v>
@@ -9195,7 +9195,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.44</v>
@@ -9631,7 +9631,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.4</v>
@@ -9852,7 +9852,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ43" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR43" t="n">
         <v>1.73</v>
@@ -10721,7 +10721,7 @@
         <v>2</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.9</v>
@@ -12029,10 +12029,10 @@
         <v>1.33</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR53" t="n">
         <v>2.15</v>
@@ -13340,7 +13340,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR59" t="n">
         <v>1.15</v>
@@ -14648,7 +14648,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ65" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR65" t="n">
         <v>1.72</v>
@@ -14863,7 +14863,7 @@
         <v>1</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.78</v>
@@ -16392,7 +16392,7 @@
         <v>2</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR73" t="n">
         <v>1.35</v>
@@ -16825,7 +16825,7 @@
         <v>0.25</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.67</v>
@@ -17918,7 +17918,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ80" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR80" t="n">
         <v>1.33</v>
@@ -18133,7 +18133,7 @@
         <v>2</v>
       </c>
       <c r="AP81" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ81" t="n">
         <v>2.22</v>
@@ -20967,7 +20967,7 @@
         <v>1.17</v>
       </c>
       <c r="AP94" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.73</v>
@@ -21403,10 +21403,10 @@
         <v>1.8</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ96" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR96" t="n">
         <v>1.32</v>
@@ -21842,7 +21842,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR98" t="n">
         <v>1.69</v>
@@ -23365,7 +23365,7 @@
         <v>0.29</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.4</v>
@@ -24022,7 +24022,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR108" t="n">
         <v>1.07</v>
@@ -24676,7 +24676,7 @@
         <v>1</v>
       </c>
       <c r="AQ111" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR111" t="n">
         <v>1.65</v>
@@ -25109,7 +25109,7 @@
         <v>0.5</v>
       </c>
       <c r="AP113" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.44</v>
@@ -27289,7 +27289,7 @@
         <v>2.2</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ123" t="n">
         <v>2.33</v>
@@ -27725,7 +27725,7 @@
         <v>1.13</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.2</v>
@@ -27946,7 +27946,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR126" t="n">
         <v>0.89</v>
@@ -28600,7 +28600,7 @@
         <v>2</v>
       </c>
       <c r="AQ129" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR129" t="n">
         <v>1.1</v>
@@ -31673,13 +31673,13 @@
         <v>3</v>
       </c>
       <c r="AX143" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY143" t="n">
         <v>6</v>
       </c>
       <c r="AZ143" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA143" t="n">
         <v>2</v>
@@ -32100,19 +32100,19 @@
         <v>2.5</v>
       </c>
       <c r="AU145" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX145" t="n">
         <v>4</v>
       </c>
-      <c r="AV145" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW145" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX145" t="n">
-        <v>5</v>
-      </c>
       <c r="AY145" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ145" t="n">
         <v>6</v>
@@ -32382,6 +32382,442 @@
       </c>
       <c r="BP146" t="n">
         <v>1.12</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="n">
+        <v>8149609</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>46082.4375</v>
+      </c>
+      <c r="F147" t="n">
+        <v>19</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Mamelodi Sundowns</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sekhukhune United</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1</v>
+      </c>
+      <c r="L147" t="n">
+        <v>3</v>
+      </c>
+      <c r="M147" t="n">
+        <v>1</v>
+      </c>
+      <c r="N147" t="n">
+        <v>4</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>['31', '81', '90+4']</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="R147" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S147" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U147" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V147" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W147" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X147" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BH147" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BI147" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BJ147" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BK147" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BL147" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BM147" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BN147" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BO147" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="BP147" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>8149611</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>46082.4375</v>
+      </c>
+      <c r="F148" t="n">
+        <v>19</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Marumo Gallants</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Durban City</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>1</v>
+      </c>
+      <c r="N148" t="n">
+        <v>1</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="R148" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S148" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="T148" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U148" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V148" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="W148" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X148" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI148" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BJ148" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BK148" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BL148" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BM148" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BN148" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BO148" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="BP148" t="n">
+        <v>1.09</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/South Africa Premier Soccer League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/South Africa Premier Soccer League_20252026.xlsx
@@ -31667,19 +31667,19 @@
         <v>3</v>
       </c>
       <c r="AV143" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX143" t="n">
         <v>8</v>
       </c>
       <c r="AY143" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ143" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA143" t="n">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/South Africa Premier Soccer League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/South Africa Premier Soccer League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP148"/>
+  <dimension ref="A1:BP151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.5</v>
@@ -1350,7 +1350,7 @@
         <v>2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.5600000000000001</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.2</v>
@@ -2440,7 +2440,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.44</v>
@@ -5928,7 +5928,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.67</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ27" t="n">
         <v>0.67</v>
@@ -6582,7 +6582,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR28" t="n">
         <v>1.62</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.78</v>
@@ -8762,7 +8762,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR38" t="n">
         <v>1.01</v>
@@ -10288,7 +10288,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR45" t="n">
         <v>0.8100000000000001</v>
@@ -10503,7 +10503,7 @@
         <v>2</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.73</v>
@@ -11160,7 +11160,7 @@
         <v>2</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR49" t="n">
         <v>1.44</v>
@@ -12683,7 +12683,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ56" t="n">
         <v>2.22</v>
@@ -13773,7 +13773,7 @@
         <v>0.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.4</v>
@@ -14209,7 +14209,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.2</v>
@@ -14430,7 +14430,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR64" t="n">
         <v>1.04</v>
@@ -15299,7 +15299,7 @@
         <v>1</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ68" t="n">
         <v>0.5</v>
@@ -15520,7 +15520,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR69" t="n">
         <v>0.8100000000000001</v>
@@ -16171,10 +16171,10 @@
         <v>0</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR72" t="n">
         <v>1.61</v>
@@ -17700,7 +17700,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ79" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR79" t="n">
         <v>1.45</v>
@@ -17915,7 +17915,7 @@
         <v>2.25</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.78</v>
@@ -19005,10 +19005,10 @@
         <v>0.5</v>
       </c>
       <c r="AP85" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR85" t="n">
         <v>1.18</v>
@@ -19880,7 +19880,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR89" t="n">
         <v>1.87</v>
@@ -21621,7 +21621,7 @@
         <v>0.2</v>
       </c>
       <c r="AP97" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ97" t="n">
         <v>0.5600000000000001</v>
@@ -21839,7 +21839,7 @@
         <v>0.83</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.2</v>
@@ -22278,7 +22278,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR100" t="n">
         <v>1.13</v>
@@ -22493,7 +22493,7 @@
         <v>1</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.2</v>
@@ -23147,7 +23147,7 @@
         <v>0.17</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.67</v>
@@ -23804,7 +23804,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ107" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR107" t="n">
         <v>0.97</v>
@@ -24237,7 +24237,7 @@
         <v>1.5</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.9</v>
@@ -24891,10 +24891,10 @@
         <v>2.5</v>
       </c>
       <c r="AP112" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR112" t="n">
         <v>1.16</v>
@@ -25112,7 +25112,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR113" t="n">
         <v>1.95</v>
@@ -25548,7 +25548,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR115" t="n">
         <v>1.9</v>
@@ -25763,7 +25763,7 @@
         <v>0.63</v>
       </c>
       <c r="AP116" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.5</v>
@@ -25981,7 +25981,7 @@
         <v>0.57</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ117" t="n">
         <v>0.67</v>
@@ -27292,7 +27292,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ123" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR123" t="n">
         <v>1.41</v>
@@ -27507,7 +27507,7 @@
         <v>0.14</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.5600000000000001</v>
@@ -28382,7 +28382,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR128" t="n">
         <v>1.53</v>
@@ -28597,7 +28597,7 @@
         <v>1.86</v>
       </c>
       <c r="AP129" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.78</v>
@@ -30126,7 +30126,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR136" t="n">
         <v>1.52</v>
@@ -30780,7 +30780,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR139" t="n">
         <v>1.94</v>
@@ -32085,7 +32085,7 @@
         <v>0.8</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.73</v>
@@ -32818,6 +32818,660 @@
       </c>
       <c r="BP148" t="n">
         <v>1.09</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="n">
+        <v>8149613</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>46084.60416666666</v>
+      </c>
+      <c r="F149" t="n">
+        <v>20</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>TS Galaxy</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Orbit College</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>2</v>
+      </c>
+      <c r="K149" t="n">
+        <v>2</v>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
+        <v>2</v>
+      </c>
+      <c r="N149" t="n">
+        <v>3</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>['22', '38']</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R149" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S149" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="T149" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U149" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V149" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="W149" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X149" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BI149" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ149" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BK149" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BM149" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BN149" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BO149" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="BP149" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="n">
+        <v>8149615</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>46084.60416666666</v>
+      </c>
+      <c r="F150" t="n">
+        <v>20</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Richards Bay</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kaizer Chiefs</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>1</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="R150" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S150" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T150" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U150" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="V150" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W150" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X150" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB150" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BE150" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BF150" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BG150" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BH150" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BI150" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BJ150" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BK150" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BL150" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BM150" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BN150" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BO150" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="BP150" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="n">
+        <v>8149616</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>46084.60416666666</v>
+      </c>
+      <c r="F151" t="n">
+        <v>20</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Siwelele</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Stellenbosch</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="R151" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S151" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T151" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U151" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V151" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W151" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X151" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BE151" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF151" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG151" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BH151" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BI151" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BJ151" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BK151" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BL151" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BM151" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="BN151" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BO151" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="BP151" t="n">
+        <v>1.11</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/South Africa Premier Soccer League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/South Africa Premier Soccer League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP151"/>
+  <dimension ref="A1:BP156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.7</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.9</v>
@@ -1786,7 +1786,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.2</v>
@@ -3094,7 +3094,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.67</v>
@@ -4838,7 +4838,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR20" t="n">
         <v>0.87</v>
@@ -5053,10 +5053,10 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR21" t="n">
         <v>1.22</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ22" t="n">
         <v>0.73</v>
@@ -5489,10 +5489,10 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR23" t="n">
         <v>1.29</v>
@@ -6800,7 +6800,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR29" t="n">
         <v>1.75</v>
@@ -7015,7 +7015,7 @@
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.2</v>
@@ -7236,7 +7236,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR31" t="n">
         <v>0.66</v>
@@ -9413,10 +9413,10 @@
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ41" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR41" t="n">
         <v>0.67</v>
@@ -9631,10 +9631,10 @@
         <v>0.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR42" t="n">
         <v>2.38</v>
@@ -9852,7 +9852,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR43" t="n">
         <v>1.73</v>
@@ -10067,7 +10067,7 @@
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.67</v>
@@ -10285,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.7</v>
@@ -10939,10 +10939,10 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR48" t="n">
         <v>1.14</v>
@@ -11157,7 +11157,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.33</v>
@@ -11378,7 +11378,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR50" t="n">
         <v>1.89</v>
@@ -12029,7 +12029,7 @@
         <v>1.33</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.2</v>
@@ -12250,7 +12250,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR54" t="n">
         <v>1.15</v>
@@ -12465,7 +12465,7 @@
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.67</v>
@@ -12686,7 +12686,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ56" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR56" t="n">
         <v>1.61</v>
@@ -13122,7 +13122,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR58" t="n">
         <v>1.83</v>
@@ -13776,7 +13776,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR61" t="n">
         <v>1.61</v>
@@ -14645,10 +14645,10 @@
         <v>3</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR65" t="n">
         <v>1.72</v>
@@ -14863,7 +14863,7 @@
         <v>1</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.78</v>
@@ -15081,10 +15081,10 @@
         <v>0.25</v>
       </c>
       <c r="AP67" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR67" t="n">
         <v>1.45</v>
@@ -15302,7 +15302,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR68" t="n">
         <v>1.48</v>
@@ -15517,7 +15517,7 @@
         <v>0.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.33</v>
@@ -16389,7 +16389,7 @@
         <v>1</v>
       </c>
       <c r="AP73" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.2</v>
@@ -17264,7 +17264,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR77" t="n">
         <v>1.12</v>
@@ -17697,7 +17697,7 @@
         <v>3</v>
       </c>
       <c r="AP79" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ79" t="n">
         <v>2</v>
@@ -17918,7 +17918,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR80" t="n">
         <v>1.33</v>
@@ -18133,10 +18133,10 @@
         <v>2</v>
       </c>
       <c r="AP81" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ81" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR81" t="n">
         <v>2.11</v>
@@ -18354,7 +18354,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR82" t="n">
         <v>1.15</v>
@@ -18569,7 +18569,7 @@
         <v>0.8</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.78</v>
@@ -18787,7 +18787,7 @@
         <v>0.6</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.2</v>
@@ -19226,7 +19226,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR86" t="n">
         <v>1.16</v>
@@ -19659,10 +19659,10 @@
         <v>0.17</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR88" t="n">
         <v>0.97</v>
@@ -20095,7 +20095,7 @@
         <v>0.8</v>
       </c>
       <c r="AP90" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.44</v>
@@ -20316,7 +20316,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ91" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR91" t="n">
         <v>1.22</v>
@@ -20749,10 +20749,10 @@
         <v>0.71</v>
       </c>
       <c r="AP93" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR93" t="n">
         <v>1.34</v>
@@ -20967,7 +20967,7 @@
         <v>1.17</v>
       </c>
       <c r="AP94" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.73</v>
@@ -21185,7 +21185,7 @@
         <v>0.67</v>
       </c>
       <c r="AP95" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ95" t="n">
         <v>0.67</v>
@@ -21406,7 +21406,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR96" t="n">
         <v>1.32</v>
@@ -21624,7 +21624,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR97" t="n">
         <v>1.16</v>
@@ -22711,10 +22711,10 @@
         <v>2</v>
       </c>
       <c r="AP102" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ102" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR102" t="n">
         <v>1.45</v>
@@ -22929,7 +22929,7 @@
         <v>1</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.73</v>
@@ -23368,7 +23368,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR105" t="n">
         <v>1.32</v>
@@ -23801,7 +23801,7 @@
         <v>3</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ107" t="n">
         <v>2</v>
@@ -24676,7 +24676,7 @@
         <v>1</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR111" t="n">
         <v>1.65</v>
@@ -25109,7 +25109,7 @@
         <v>0.5</v>
       </c>
       <c r="AP113" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.7</v>
@@ -25330,7 +25330,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR114" t="n">
         <v>1.9</v>
@@ -25766,7 +25766,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR116" t="n">
         <v>1.02</v>
@@ -26420,7 +26420,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ119" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR119" t="n">
         <v>1.83</v>
@@ -26635,7 +26635,7 @@
         <v>1</v>
       </c>
       <c r="AP120" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.73</v>
@@ -26853,7 +26853,7 @@
         <v>1.43</v>
       </c>
       <c r="AP121" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ121" t="n">
         <v>1.44</v>
@@ -27510,7 +27510,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR124" t="n">
         <v>1.63</v>
@@ -27943,7 +27943,7 @@
         <v>1.13</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.2</v>
@@ -28029,7 +28029,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>8171465</v>
+        <v>8149580</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -28045,201 +28045,201 @@
         <v>46053.54166666666</v>
       </c>
       <c r="F127" t="n">
+        <v>17</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Polokwane City</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Orbit College</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>2</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>2</v>
+      </c>
+      <c r="L127" t="n">
+        <v>2</v>
+      </c>
+      <c r="M127" t="n">
+        <v>2</v>
+      </c>
+      <c r="N127" t="n">
+        <v>4</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>['26', '43']</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>['51', '87']</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S127" t="n">
         <v>6</v>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Orlando Pirates</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Magesi</t>
-        </is>
-      </c>
-      <c r="I127" t="n">
-        <v>2</v>
-      </c>
-      <c r="J127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" t="n">
-        <v>2</v>
-      </c>
-      <c r="L127" t="n">
-        <v>2</v>
-      </c>
-      <c r="M127" t="n">
-        <v>0</v>
-      </c>
-      <c r="N127" t="n">
-        <v>2</v>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>['9', '41']</t>
-        </is>
-      </c>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q127" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R127" t="n">
+      <c r="T127" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U127" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V127" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="W127" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X127" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BJ127" t="n">
         <v>2.05</v>
       </c>
-      <c r="S127" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="T127" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U127" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V127" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W127" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X127" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y127" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z127" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA127" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB127" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC127" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD127" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE127" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF127" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG127" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH127" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI127" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AJ127" t="n">
+      <c r="BK127" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BN127" t="n">
         <v>1.36</v>
       </c>
-      <c r="AK127" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AL127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM127" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AN127" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO127" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AP127" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AQ127" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AR127" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS127" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AT127" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AU127" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV127" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW127" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX127" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY127" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ127" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA127" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB127" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC127" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD127" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BE127" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF127" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG127" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BH127" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="BI127" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BJ127" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BK127" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BL127" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BM127" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BN127" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BO127" t="n">
-        <v>4.62</v>
+        <v>3.91</v>
       </c>
       <c r="BP127" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="128">
@@ -28247,7 +28247,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>8149580</v>
+        <v>8171465</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -28263,16 +28263,16 @@
         <v>46053.54166666666</v>
       </c>
       <c r="F128" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -28288,176 +28288,176 @@
         <v>2</v>
       </c>
       <c r="M128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
+        <v>2</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>['9', '41']</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R128" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S128" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="T128" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U128" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V128" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W128" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X128" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA128" t="n">
         <v>4</v>
       </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>['26', '43']</t>
-        </is>
-      </c>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>['51', '87']</t>
-        </is>
-      </c>
-      <c r="Q128" t="n">
+      <c r="AB128" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AN128" t="n">
         <v>2.5</v>
       </c>
-      <c r="R128" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S128" t="n">
+      <c r="AO128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU128" t="n">
         <v>6</v>
       </c>
-      <c r="T128" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U128" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V128" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="W128" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X128" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA128" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="AC128" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD128" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE128" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF128" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG128" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH128" t="n">
+      <c r="AV128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BN128" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI128" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ128" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AK128" t="n">
+      <c r="BO128" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="BP128" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AL128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM128" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AN128" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AO128" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AP128" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AQ128" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AR128" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS128" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AT128" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU128" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV128" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW128" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX128" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY128" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ128" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA128" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB128" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC128" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD128" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BE128" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF128" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BG128" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BH128" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="BI128" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BJ128" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BK128" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BL128" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BM128" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="BN128" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BO128" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="BP128" t="n">
-        <v>1.17</v>
       </c>
     </row>
     <row r="129">
@@ -28600,7 +28600,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR129" t="n">
         <v>1.1</v>
@@ -28815,10 +28815,10 @@
         <v>2</v>
       </c>
       <c r="AP130" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ130" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR130" t="n">
         <v>1.11</v>
@@ -29033,7 +29033,7 @@
         <v>0.89</v>
       </c>
       <c r="AP131" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.73</v>
@@ -29254,7 +29254,7 @@
         <v>1</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR132" t="n">
         <v>1.79</v>
@@ -29472,7 +29472,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR133" t="n">
         <v>1.97</v>
@@ -29687,7 +29687,7 @@
         <v>0.63</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.67</v>
@@ -29905,7 +29905,7 @@
         <v>0.86</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ135" t="n">
         <v>0.78</v>
@@ -30562,7 +30562,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR138" t="n">
         <v>1.29</v>
@@ -30995,7 +30995,7 @@
         <v>1.78</v>
       </c>
       <c r="AP140" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.9</v>
@@ -31081,7 +31081,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>8149601</v>
+        <v>8149599</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -31101,197 +31101,197 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K141" t="n">
         <v>1</v>
       </c>
       <c r="L141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '73']</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="R141" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="S141" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="T141" t="n">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="U141" t="n">
-        <v>2.33</v>
+        <v>1.98</v>
       </c>
       <c r="V141" t="n">
-        <v>3.58</v>
+        <v>4.4</v>
       </c>
       <c r="W141" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="X141" t="n">
-        <v>8.1</v>
+        <v>10.5</v>
       </c>
       <c r="Y141" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Z141" t="n">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="AA141" t="n">
-        <v>2.87</v>
+        <v>2.55</v>
       </c>
       <c r="AB141" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AC141" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AD141" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="AE141" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM141" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF141" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AG141" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH141" t="n">
+      <c r="AN141" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ141" t="n">
         <v>1.44</v>
       </c>
-      <c r="AI141" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ141" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AK141" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM141" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AN141" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AO141" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AP141" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ141" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AR141" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AS141" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AT141" t="n">
-        <v>2.31</v>
+        <v>2.97</v>
       </c>
       <c r="AU141" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY141" t="n">
         <v>7</v>
       </c>
-      <c r="AV141" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW141" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX141" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY141" t="n">
-        <v>16</v>
-      </c>
       <c r="AZ141" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="BA141" t="n">
         <v>2</v>
       </c>
       <c r="BB141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD141" t="n">
-        <v>1.46</v>
+        <v>1.92</v>
       </c>
       <c r="BE141" t="n">
-        <v>8.5</v>
+        <v>6.1</v>
       </c>
       <c r="BF141" t="n">
-        <v>3.25</v>
+        <v>2.37</v>
       </c>
       <c r="BG141" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="BH141" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="BI141" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BL141" t="n">
         <v>1.65</v>
       </c>
-      <c r="BJ141" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BK141" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BL141" t="n">
-        <v>1.67</v>
-      </c>
       <c r="BM141" t="n">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="BN141" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO141" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="BP141" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="142">
@@ -31299,7 +31299,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>8149599</v>
+        <v>8149601</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -31319,197 +31319,197 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K142" t="n">
         <v>1</v>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>['24', '73']</t>
-        </is>
-      </c>
       <c r="Q142" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="R142" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="S142" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T142" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U142" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="V142" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="W142" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X142" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BO142" t="n">
         <v>3.8</v>
       </c>
-      <c r="T142" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U142" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V142" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W142" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X142" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y142" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z142" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AA142" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AC142" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD142" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE142" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF142" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG142" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH142" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI142" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AJ142" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AK142" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AL142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM142" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN142" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AO142" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP142" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ142" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR142" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS142" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AT142" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AU142" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV142" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW142" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX142" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY142" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ142" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA142" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB142" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC142" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD142" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BE142" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="BF142" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="BG142" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BH142" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="BI142" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BJ142" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BK142" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BL142" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BM142" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="BN142" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BO142" t="n">
-        <v>3.91</v>
-      </c>
       <c r="BP142" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="143">
@@ -31652,7 +31652,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ143" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR143" t="n">
         <v>1.93</v>
@@ -32521,10 +32521,10 @@
         <v>2</v>
       </c>
       <c r="AP147" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR147" t="n">
         <v>1.89</v>
@@ -32757,7 +32757,7 @@
         <v>1</v>
       </c>
       <c r="AV148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW148" t="n">
         <v>5</v>
@@ -32769,7 +32769,7 @@
         <v>6</v>
       </c>
       <c r="AZ148" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA148" t="n">
         <v>4</v>
@@ -32972,7 +32972,7 @@
         <v>2.31</v>
       </c>
       <c r="AU149" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV149" t="n">
         <v>2</v>
@@ -32984,7 +32984,7 @@
         <v>2</v>
       </c>
       <c r="AY149" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ149" t="n">
         <v>4</v>
@@ -33196,13 +33196,13 @@
         <v>0</v>
       </c>
       <c r="AW150" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX150" t="n">
         <v>4</v>
       </c>
       <c r="AY150" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ150" t="n">
         <v>4</v>
@@ -33411,7 +33411,7 @@
         <v>2</v>
       </c>
       <c r="AV151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW151" t="n">
         <v>10</v>
@@ -33423,7 +33423,7 @@
         <v>12</v>
       </c>
       <c r="AZ151" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA151" t="n">
         <v>4</v>
@@ -33472,6 +33472,1096 @@
       </c>
       <c r="BP151" t="n">
         <v>1.11</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="n">
+        <v>8149621</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>46085.60416666666</v>
+      </c>
+      <c r="F152" t="n">
+        <v>20</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Mamelodi Sundowns</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Golden Arrows</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>1</v>
+      </c>
+      <c r="L152" t="n">
+        <v>2</v>
+      </c>
+      <c r="M152" t="n">
+        <v>1</v>
+      </c>
+      <c r="N152" t="n">
+        <v>3</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>['28', '48']</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R152" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U152" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V152" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W152" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X152" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH152" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BI152" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BJ152" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BK152" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BL152" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BM152" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BN152" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO152" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP152" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="n">
+        <v>8149623</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>46085.60416666666</v>
+      </c>
+      <c r="F153" t="n">
+        <v>20</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>AmaZulu</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Magesi</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R153" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S153" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="T153" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U153" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V153" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W153" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X153" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD153" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BE153" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="BF153" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG153" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH153" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BI153" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ153" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BK153" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BL153" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BM153" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BN153" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BO153" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BP153" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="n">
+        <v>8149624</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>46085.60416666666</v>
+      </c>
+      <c r="F154" t="n">
+        <v>20</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Chippa United</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Marumo Gallants</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>1</v>
+      </c>
+      <c r="L154" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" t="n">
+        <v>3</v>
+      </c>
+      <c r="N154" t="n">
+        <v>4</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>['53', '64', '81']</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="R154" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S154" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T154" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U154" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="V154" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W154" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X154" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BG154" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BH154" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BI154" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BJ154" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BK154" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BL154" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BM154" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BN154" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BO154" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="BP154" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="n">
+        <v>8149618</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>46085.60416666666</v>
+      </c>
+      <c r="F155" t="n">
+        <v>20</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Durban City</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sekhukhune United</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="n">
+        <v>1</v>
+      </c>
+      <c r="N155" t="n">
+        <v>2</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R155" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S155" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="T155" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U155" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V155" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W155" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X155" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BI155" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BJ155" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BK155" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BL155" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BM155" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="BN155" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BO155" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BP155" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="n">
+        <v>8149620</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>46085.60416666666</v>
+      </c>
+      <c r="F156" t="n">
+        <v>20</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Polokwane City</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Orlando Pirates</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" t="n">
+        <v>2</v>
+      </c>
+      <c r="N156" t="n">
+        <v>3</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>['52', '90']</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R156" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S156" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T156" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U156" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V156" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W156" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X156" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>31</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BG156" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BH156" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BI156" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BJ156" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BK156" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BL156" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BM156" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BN156" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BO156" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="BP156" t="n">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/South Africa Premier Soccer League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/South Africa Premier Soccer League_20252026.xlsx
@@ -33043,7 +33043,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>8149615</v>
+        <v>8149616</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -33063,12 +33063,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -33081,17 +33081,17 @@
         <v>0</v>
       </c>
       <c r="L150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -33100,157 +33100,157 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>4.69</v>
+        <v>3.59</v>
       </c>
       <c r="R150" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="S150" t="n">
-        <v>2.77</v>
+        <v>4.1</v>
       </c>
       <c r="T150" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U150" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="V150" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="W150" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X150" t="n">
-        <v>9.1</v>
+        <v>17</v>
       </c>
       <c r="Y150" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z150" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA150" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="AB150" t="n">
-        <v>1.91</v>
+        <v>2.99</v>
       </c>
       <c r="AC150" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AD150" t="n">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="AE150" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AF150" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="AG150" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="AH150" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AI150" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="AJ150" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AK150" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL150" t="n">
         <v>0</v>
       </c>
       <c r="AM150" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AN150" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AO150" t="n">
-        <v>2.33</v>
+        <v>1.38</v>
       </c>
       <c r="AP150" t="n">
         <v>1.6</v>
       </c>
       <c r="AQ150" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.95</v>
+        <v>1.27</v>
       </c>
       <c r="AT150" t="n">
-        <v>3.55</v>
+        <v>2.51</v>
       </c>
       <c r="AU150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB150" t="n">
         <v>7</v>
       </c>
-      <c r="AV150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW150" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX150" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY150" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ150" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA150" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB150" t="n">
-        <v>5</v>
-      </c>
       <c r="BC150" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BD150" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="BE150" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF150" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="BG150" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BH150" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="BI150" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="BJ150" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="BK150" t="n">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="BL150" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="BM150" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="BN150" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO150" t="n">
-        <v>4.62</v>
+        <v>4.66</v>
       </c>
       <c r="BP150" t="n">
         <v>1.11</v>
@@ -33261,7 +33261,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>8149616</v>
+        <v>8149615</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -33281,12 +33281,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="I151" t="n">
@@ -33299,176 +33299,176 @@
         <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="Q151" t="n">
-        <v>3.59</v>
+        <v>4.69</v>
       </c>
       <c r="R151" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S151" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T151" t="n">
         <v>1.64</v>
       </c>
-      <c r="S151" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T151" t="n">
-        <v>1.67</v>
-      </c>
       <c r="U151" t="n">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="V151" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="W151" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X151" t="n">
-        <v>17</v>
+        <v>9.1</v>
       </c>
       <c r="Y151" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z151" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA151" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AB151" t="n">
-        <v>2.99</v>
+        <v>1.91</v>
       </c>
       <c r="AC151" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AD151" t="n">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AF151" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="AG151" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="AH151" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AI151" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="AJ151" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AK151" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL151" t="n">
         <v>0</v>
       </c>
       <c r="AM151" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AN151" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AO151" t="n">
-        <v>1.38</v>
+        <v>2.33</v>
       </c>
       <c r="AP151" t="n">
         <v>1.6</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.27</v>
+        <v>1.95</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.51</v>
+        <v>3.55</v>
       </c>
       <c r="AU151" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AV151" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW151" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA151" t="n">
         <v>10</v>
       </c>
-      <c r="AX151" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY151" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ151" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA151" t="n">
-        <v>4</v>
-      </c>
       <c r="BB151" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BC151" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BD151" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="BE151" t="n">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="BF151" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="BG151" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="BH151" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="BI151" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="BJ151" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="BK151" t="n">
-        <v>2.85</v>
+        <v>2.43</v>
       </c>
       <c r="BL151" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="BM151" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="BN151" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BO151" t="n">
-        <v>4.66</v>
+        <v>4.62</v>
       </c>
       <c r="BP151" t="n">
         <v>1.11</v>
@@ -33629,7 +33629,7 @@
         <v>4</v>
       </c>
       <c r="AV152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW152" t="n">
         <v>9</v>
@@ -33641,7 +33641,7 @@
         <v>13</v>
       </c>
       <c r="AZ152" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA152" t="n">
         <v>5</v>
@@ -33853,13 +33853,13 @@
         <v>4</v>
       </c>
       <c r="AX153" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY153" t="n">
         <v>6</v>
       </c>
       <c r="AZ153" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA153" t="n">
         <v>4</v>
@@ -34062,19 +34062,19 @@
         <v>2.24</v>
       </c>
       <c r="AU154" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV154" t="n">
         <v>5</v>
       </c>
       <c r="AW154" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX154" t="n">
         <v>5</v>
       </c>
       <c r="AY154" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ154" t="n">
         <v>10</v>
@@ -34083,10 +34083,10 @@
         <v>5</v>
       </c>
       <c r="BB154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC154" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD154" t="n">
         <v>1.64</v>
@@ -34504,13 +34504,13 @@
         <v>12</v>
       </c>
       <c r="AW156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX156" t="n">
         <v>19</v>
       </c>
       <c r="AY156" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ156" t="n">
         <v>31</v>

--- a/Bases_de_Dados/FootyStats/South Africa Premier Soccer League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/South Africa Premier Soccer League_20252026.xlsx
@@ -33853,13 +33853,13 @@
         <v>4</v>
       </c>
       <c r="AX153" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY153" t="n">
         <v>6</v>
       </c>
       <c r="AZ153" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA153" t="n">
         <v>4</v>
@@ -34501,7 +34501,7 @@
         <v>3</v>
       </c>
       <c r="AV156" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW156" t="n">
         <v>2</v>
@@ -34513,7 +34513,7 @@
         <v>5</v>
       </c>
       <c r="AZ156" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BA156" t="n">
         <v>2</v>
